--- a/BRIN 3219/Mayo/BRIN3219-EXPENSAS-MAYO}.xlsx
+++ b/BRIN 3219/Mayo/BRIN3219-EXPENSAS-MAYO}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRIN 3219\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA8ABFD0-D8D1-40B2-993D-D6E21528664F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92574E53-6E0E-4603-AEC4-7801896C9B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="RESUMEN" sheetId="27" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$N$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$116</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$N$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="162">
   <si>
     <t>U.F.</t>
   </si>
@@ -465,39 +465,21 @@
     <t>Asignacion remunerativa</t>
   </si>
   <si>
-    <t>JPL - Articulo de limpiezas</t>
-  </si>
-  <si>
     <t>Ingreso por pago de Expensas - MARZO</t>
   </si>
   <si>
-    <t>Diferencia mes anterior honorarios Sr Gustavo Padron - Contador</t>
-  </si>
-  <si>
     <t>HORAS EXTRAS FUMIGACION</t>
   </si>
   <si>
-    <t xml:space="preserve">Ezequiel Sarro - contestacion apelacion piso 5 </t>
-  </si>
-  <si>
     <t>3-SERVICIOS COMUNES</t>
   </si>
   <si>
-    <t xml:space="preserve">AYSA - Cuota 3 del plan de pago adeudado </t>
-  </si>
-  <si>
     <t>4- MANTENIMIENTO DE PARTES COMUNES</t>
   </si>
   <si>
     <t>5- GASTO DE ADMINISTRACION</t>
   </si>
   <si>
-    <t>AYSA - Vto 1/4</t>
-  </si>
-  <si>
-    <t>SE DEBE AYSA CON VTO 30/04</t>
-  </si>
-  <si>
     <t>6-SEGUROS OBLIGATORIOS</t>
   </si>
   <si>
@@ -513,18 +495,9 @@
     <t>GASTOS EXTR. ASCENSOR Y LIBROS</t>
   </si>
   <si>
-    <t>Ezequiel</t>
-  </si>
-  <si>
-    <t>Julio doartero</t>
-  </si>
-  <si>
     <t>MAYO</t>
   </si>
   <si>
-    <t>Horas extra fumigacion - Marzo y MAYO</t>
-  </si>
-  <si>
     <t>Damato fumigaciones - MAYO</t>
   </si>
   <si>
@@ -532,6 +505,30 @@
   </si>
   <si>
     <t>VTO: 16/05</t>
+  </si>
+  <si>
+    <t>Caleb - Trabajo de plomeria, arreglo de contactora, revision de tanques y reparacion de automaticos 12/05</t>
+  </si>
+  <si>
+    <t>Ezequiel Sarro - escrito presentado ante la camara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julio doartero - visitas de emergencia falta de agua </t>
+  </si>
+  <si>
+    <t>Horas extra fumigacion</t>
+  </si>
+  <si>
+    <t>AYSA - Vto 30/04</t>
+  </si>
+  <si>
+    <t>Acuerdo banco galicia con el estudio palmero de belizan y asociados por el embargo de la cuenta realizado por la Sra. Elena Graciela</t>
+  </si>
+  <si>
+    <t>Colocacion ceramicos en el 1er piso - Fernando Parra</t>
+  </si>
+  <si>
+    <t>EN MAY LOS CERRAMOS ADEUDANDO LOS SINDICATOS YA QUE SE NOS PASO PAGARLOS</t>
   </si>
 </sst>
 </file>
@@ -539,16 +536,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -734,13 +731,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
@@ -756,21 +746,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -826,7 +801,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -1212,17 +1187,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -1357,18 +1321,18 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1377,16 +1341,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1401,7 +1365,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1411,10 +1375,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1443,13 +1407,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1461,38 +1425,38 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1500,114 +1464,102 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="3" fillId="3" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1615,8 +1567,8 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1626,10 +1578,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1637,45 +1588,26 @@
     <xf numFmtId="10" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="10" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="22" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1687,12 +1619,81 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1717,12 +1718,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1732,15 +1727,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1750,91 +1736,36 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="31" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="32" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1865,7 +1796,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>200025</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>151559</xdr:rowOff>
     </xdr:to>
@@ -2282,81 +2213,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="26.25" customHeight="1">
-      <c r="A1" s="104"/>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106" t="s">
+      <c r="A1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="107" t="str">
+      <c r="F1" s="106" t="str">
         <f>RESUMEN!F8</f>
         <v>MAYO</v>
       </c>
-      <c r="G1" s="108" t="str">
+      <c r="G1" s="107" t="str">
         <f>RESUMEN!G8</f>
         <v>VTO: 16/05</v>
       </c>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="109"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="108"/>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
-      <c r="C2" s="129">
+      <c r="C2" s="128">
         <v>1333150</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
       <c r="L2" s="61"/>
       <c r="M2" s="61"/>
       <c r="N2" s="61"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="103">
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="102">
         <v>1886797.93</v>
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
       <c r="L3" s="61" t="s">
         <v>81</v>
       </c>
@@ -2364,24 +2294,24 @@
       <c r="N3" s="61"/>
     </row>
     <row r="4" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A4" s="120"/>
-      <c r="B4" s="121" t="s">
+      <c r="A4" s="119"/>
+      <c r="B4" s="120" t="s">
         <v>82</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
-      <c r="E4" s="121" t="s">
+      <c r="E4" s="120" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="125">
+      <c r="F4" s="124">
         <f>105400+260-8</f>
         <v>105652</v>
       </c>
-      <c r="G4" s="119"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="119"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="119"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
       <c r="L4" s="61" t="s">
         <v>80</v>
       </c>
@@ -2389,155 +2319,158 @@
       <c r="N4" s="61"/>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A5" s="122"/>
-      <c r="B5" s="189">
+      <c r="A5" s="121"/>
+      <c r="B5" s="171">
         <f>C3</f>
         <v>1886797.93</v>
       </c>
-      <c r="C5" s="189"/>
+      <c r="C5" s="171"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="123">
+      <c r="E5" s="122">
         <v>70000</v>
       </c>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="116"/>
-      <c r="K5" s="116"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
       <c r="L5" s="61"/>
       <c r="M5" s="61"/>
       <c r="N5" s="61"/>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A6" s="122"/>
-      <c r="B6" s="124" t="s">
+      <c r="A6" s="121"/>
+      <c r="B6" s="123" t="s">
         <v>83</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="121" t="s">
+      <c r="E6" s="120" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="116"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
       <c r="L6" s="61"/>
       <c r="M6" s="61"/>
       <c r="N6" s="61"/>
     </row>
     <row r="7" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A7" s="122"/>
-      <c r="B7" s="189">
+      <c r="A7" s="121"/>
+      <c r="B7" s="171">
         <v>1800000</v>
       </c>
-      <c r="C7" s="189"/>
+      <c r="C7" s="171"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
-      <c r="F7" s="116"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="116"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+      <c r="K7" s="115"/>
       <c r="L7" s="61"/>
       <c r="M7" s="61"/>
       <c r="N7" s="61"/>
     </row>
     <row r="8" spans="1:14" ht="53.25" customHeight="1" thickBot="1">
-      <c r="A8" s="110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="111" t="s">
+      <c r="A8" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="112" t="s">
+      <c r="C8" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="113" t="s">
+      <c r="D8" s="112" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="111" t="s">
+      <c r="E8" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="114" t="s">
+      <c r="F8" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="114" t="s">
+      <c r="G8" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="114" t="s">
+      <c r="H8" s="113" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="J8" s="114" t="s">
+      <c r="I8" s="113" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="128" t="s">
+      <c r="K8" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="L8" s="111" t="s">
+      <c r="L8" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="M8" s="111" t="s">
-        <v>155</v>
-      </c>
-      <c r="N8" s="115" t="s">
+      <c r="M8" s="110" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" s="114" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
-      <c r="A9" s="166">
+      <c r="A9" s="227">
         <v>1</v>
       </c>
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="223" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="162" t="s">
+      <c r="C9" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="162" t="s">
+      <c r="D9" s="224" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="163">
+      <c r="E9" s="225">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="F9" s="155">
-        <v>483124.75750197738</v>
-      </c>
-      <c r="G9" s="167"/>
-      <c r="H9" s="157">
+      <c r="F9" s="99">
+        <v>654594.59569455055</v>
+      </c>
+      <c r="G9" s="228">
+        <f>F9</f>
+        <v>654594.59569455055</v>
+      </c>
+      <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>483124.75750197738</v>
-      </c>
-      <c r="I9" s="157">
+        <v>0</v>
+      </c>
+      <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>17875.616027573167</v>
-      </c>
-      <c r="J9" s="157">
+        <v>0</v>
+      </c>
+      <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="157">
+      <c r="K9" s="68">
         <f>F$4*E9</f>
         <v>4278.9059999999999</v>
       </c>
-      <c r="L9" s="158">
+      <c r="L9" s="226">
         <f>B$5*E9</f>
         <v>76415.316164999997</v>
       </c>
-      <c r="M9" s="158">
+      <c r="M9" s="226">
         <f>B$7*E9</f>
         <v>72900</v>
       </c>
-      <c r="N9" s="158">
+      <c r="N9" s="226">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>654594.59569455055</v>
+        <v>153594.22216499998</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -2555,11 +2488,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>192576.87662399997</v>
-      </c>
-      <c r="G10" s="168">
+        <v>245750.75546399999</v>
+      </c>
+      <c r="G10" s="160">
         <f>F10</f>
-        <v>192576.87662399997</v>
+        <v>245750.75546399999</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -2591,101 +2524,104 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
-      <c r="A11" s="151">
+      <c r="A11" s="222">
         <v>3</v>
       </c>
-      <c r="B11" s="165" t="s">
+      <c r="B11" s="223" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="162" t="s">
+      <c r="C11" s="224" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="162" t="s">
+      <c r="D11" s="224" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="163">
+      <c r="E11" s="225">
         <v>4.82E-2</v>
       </c>
-      <c r="F11" s="155">
-        <v>583476.22770083812</v>
-      </c>
-      <c r="G11" s="169"/>
-      <c r="H11" s="157">
+      <c r="F11" s="99">
+        <v>787860.93475176918</v>
+      </c>
+      <c r="G11" s="160">
+        <f>606000+182796</f>
+        <v>788796</v>
+      </c>
+      <c r="H11" s="68">
         <f t="shared" si="0"/>
-        <v>583476.22770083812</v>
-      </c>
-      <c r="I11" s="157">
+        <v>0</v>
+      </c>
+      <c r="I11" s="68">
         <f t="shared" ref="I11:I31" si="6">H11*3.7%</f>
-        <v>21588.620424931014</v>
-      </c>
-      <c r="J11" s="157">
+        <v>0</v>
+      </c>
+      <c r="J11" s="68">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="157">
+        <v>935.06524823082145</v>
+      </c>
+      <c r="K11" s="68">
         <f t="shared" si="2"/>
         <v>5092.4264000000003</v>
       </c>
-      <c r="L11" s="158">
+      <c r="L11" s="226">
         <f t="shared" si="3"/>
         <v>90943.660225999993</v>
       </c>
-      <c r="M11" s="158">
+      <c r="M11" s="226">
         <f t="shared" si="4"/>
         <v>86760</v>
       </c>
-      <c r="N11" s="158">
+      <c r="N11" s="226">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>787860.93475176918</v>
+        <v>181861.02137776918</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
-      <c r="A12" s="151">
+      <c r="A12" s="147">
         <v>4</v>
       </c>
-      <c r="B12" s="164" t="s">
+      <c r="B12" s="159" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="162" t="s">
+      <c r="C12" s="157" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="162" t="s">
+      <c r="D12" s="157" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="163">
+      <c r="E12" s="158">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="155">
-        <v>1080001.7229162182</v>
-      </c>
-      <c r="G12" s="169"/>
-      <c r="H12" s="157">
+      <c r="F12" s="151">
+        <v>1322857.8579191184</v>
+      </c>
+      <c r="G12" s="161"/>
+      <c r="H12" s="152">
         <f t="shared" si="0"/>
-        <v>1080001.7229162182</v>
-      </c>
-      <c r="I12" s="157">
+        <v>1322857.8579191184</v>
+      </c>
+      <c r="I12" s="152">
         <f t="shared" si="6"/>
-        <v>39960.06374790008</v>
-      </c>
-      <c r="J12" s="157">
+        <v>48945.740743007387</v>
+      </c>
+      <c r="J12" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="157">
+      <c r="K12" s="152">
         <f t="shared" si="2"/>
         <v>5652.3819999999996</v>
       </c>
-      <c r="L12" s="158">
+      <c r="L12" s="153">
         <f t="shared" si="3"/>
         <v>100943.68925499999</v>
       </c>
-      <c r="M12" s="158">
+      <c r="M12" s="153">
         <f t="shared" si="4"/>
         <v>96300</v>
       </c>
-      <c r="N12" s="158">
+      <c r="N12" s="153">
         <f t="shared" si="5"/>
-        <v>1322857.8579191184</v>
+        <v>1574699.6699171257</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -2703,11 +2639,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>114416.81713</v>
-      </c>
-      <c r="G13" s="168">
+        <v>146009.32230499998</v>
+      </c>
+      <c r="G13" s="160">
         <f>F13</f>
-        <v>114416.81713</v>
+        <v>146009.32230499998</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -2755,11 +2691,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>106689.96714200001</v>
-      </c>
-      <c r="G14" s="168">
+        <v>136148.952487</v>
+      </c>
+      <c r="G14" s="160">
         <f>F14</f>
-        <v>106689.96714200001</v>
+        <v>136148.952487</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -2807,19 +2743,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>123035.22673199998</v>
-      </c>
-      <c r="G15" s="168">
-        <f>F15</f>
-        <v>123035.22673199998</v>
+        <v>157007.42710199999</v>
+      </c>
+      <c r="G15" s="160">
+        <v>157000</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.4271019999869168</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.27480277399951597</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
@@ -2839,7 +2774,7 @@
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>157007.42710199999</v>
+        <v>157015.12900677399</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -2859,11 +2794,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>307772.94998337491</v>
-      </c>
-      <c r="G16" s="168">
+        <v>202896.07125499999</v>
+      </c>
+      <c r="G16" s="160">
         <f>F16</f>
-        <v>307772.94998337491</v>
+        <v>202896.07125499999</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -2911,11 +2846,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>114416.81713</v>
-      </c>
-      <c r="G17" s="168">
+        <v>146009.32230499998</v>
+      </c>
+      <c r="G17" s="160">
         <f>F17</f>
-        <v>114416.81713</v>
+        <v>146009.32230499998</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
@@ -2947,99 +2882,101 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1">
-      <c r="A18" s="151">
+      <c r="A18" s="147">
         <v>10</v>
       </c>
-      <c r="B18" s="159" t="s">
+      <c r="B18" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="160" t="s">
+      <c r="C18" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="162"/>
-      <c r="E18" s="163">
+      <c r="D18" s="157"/>
+      <c r="E18" s="158">
         <v>3.5900000000000001E-2</v>
       </c>
-      <c r="F18" s="155">
-        <v>869519.26690976229</v>
-      </c>
-      <c r="G18" s="169"/>
-      <c r="H18" s="157">
+      <c r="F18" s="151">
+        <v>1037840.4322724235</v>
+      </c>
+      <c r="G18" s="161">
+        <v>400000</v>
+      </c>
+      <c r="H18" s="152">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>869519.26690976229</v>
-      </c>
-      <c r="I18" s="157">
+        <v>637840.43227242352</v>
+      </c>
+      <c r="I18" s="152">
         <f t="shared" si="6"/>
-        <v>32172.212875661207</v>
-      </c>
-      <c r="J18" s="157">
+        <v>23600.095994079675</v>
+      </c>
+      <c r="J18" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K18" s="157">
+      <c r="K18" s="152">
         <f t="shared" si="2"/>
         <v>3792.9068000000002</v>
       </c>
-      <c r="L18" s="158">
+      <c r="L18" s="153">
         <f t="shared" si="3"/>
         <v>67736.045687000005</v>
       </c>
-      <c r="M18" s="158">
+      <c r="M18" s="153">
         <f t="shared" si="4"/>
         <v>64620</v>
       </c>
-      <c r="N18" s="158">
+      <c r="N18" s="153">
         <f t="shared" si="5"/>
-        <v>1037840.4322724235</v>
+        <v>797589.48075350327</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
-      <c r="A19" s="151">
+      <c r="A19" s="147">
         <v>11</v>
       </c>
-      <c r="B19" s="159" t="s">
+      <c r="B19" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="160" t="s">
+      <c r="C19" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="162" t="s">
+      <c r="D19" s="157" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="163">
+      <c r="E19" s="158">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="155">
-        <v>617568.15854423842</v>
-      </c>
-      <c r="G19" s="169"/>
-      <c r="H19" s="157">
+      <c r="F19" s="151">
+        <v>797425.60751237522</v>
+      </c>
+      <c r="G19" s="161"/>
+      <c r="H19" s="152">
         <f t="shared" si="0"/>
-        <v>617568.15854423842</v>
-      </c>
-      <c r="I19" s="157">
+        <v>797425.60751237522</v>
+      </c>
+      <c r="I19" s="152">
         <f t="shared" si="6"/>
-        <v>22850.021866136824</v>
-      </c>
-      <c r="J19" s="157">
+        <v>29504.747477957888</v>
+      </c>
+      <c r="J19" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="157">
+      <c r="K19" s="152">
         <f t="shared" si="2"/>
         <v>4373.9928</v>
       </c>
-      <c r="L19" s="158">
+      <c r="L19" s="153">
         <f t="shared" si="3"/>
         <v>78113.434301999994</v>
       </c>
-      <c r="M19" s="158">
+      <c r="M19" s="153">
         <f t="shared" si="4"/>
         <v>74520</v>
       </c>
-      <c r="N19" s="158">
+      <c r="N19" s="153">
         <f t="shared" si="5"/>
-        <v>797425.60751237522</v>
+        <v>983937.78209233307</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -3049,7 +2986,7 @@
       <c r="B20" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="102" t="s">
+      <c r="C20" s="101" t="s">
         <v>124</v>
       </c>
       <c r="D20" s="97" t="s">
@@ -3059,11 +2996,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>158994.79783</v>
-      </c>
-      <c r="G20" s="168">
+        <v>202896.07125499999</v>
+      </c>
+      <c r="G20" s="160">
         <f>F20</f>
-        <v>158994.79783</v>
+        <v>202896.07125499999</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -3095,54 +3032,52 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1">
-      <c r="A21" s="151">
+      <c r="A21" s="147">
         <v>13</v>
       </c>
-      <c r="B21" s="159" t="s">
+      <c r="B21" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="160" t="s">
+      <c r="C21" s="155" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="160" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="161">
+      <c r="D21" s="155" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="156">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="155">
-        <v>371671.79901799065</v>
-      </c>
-      <c r="G21" s="169">
-        <v>60243.197629999995</v>
-      </c>
-      <c r="H21" s="157">
+      <c r="F21" s="151">
+        <v>468960.78194434626</v>
+      </c>
+      <c r="G21" s="161"/>
+      <c r="H21" s="152">
         <f t="shared" si="0"/>
-        <v>311428.60138799064</v>
-      </c>
-      <c r="I21" s="157">
+        <v>468960.78194434626</v>
+      </c>
+      <c r="I21" s="152">
         <f t="shared" si="6"/>
-        <v>11522.858251355656</v>
-      </c>
-      <c r="J21" s="157">
+        <v>17351.548931940815</v>
+      </c>
+      <c r="J21" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="157">
+      <c r="K21" s="152">
         <f t="shared" si="2"/>
         <v>4067.6019999999999</v>
       </c>
-      <c r="L21" s="158">
+      <c r="L21" s="153">
         <f t="shared" si="3"/>
         <v>72641.720304999995</v>
       </c>
-      <c r="M21" s="158">
+      <c r="M21" s="153">
         <f t="shared" si="4"/>
         <v>69300</v>
       </c>
-      <c r="N21" s="158">
+      <c r="N21" s="153">
         <f t="shared" si="5"/>
-        <v>468960.78194434626</v>
+        <v>632321.65318128711</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -3162,11 +3097,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>106689.96714200001</v>
-      </c>
-      <c r="G22" s="168">
+        <v>136148.952487</v>
+      </c>
+      <c r="G22" s="160">
         <f>F22</f>
-        <v>106689.96714200001</v>
+        <v>136148.952487</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -3214,11 +3149,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>123035.22673199998</v>
-      </c>
-      <c r="G23" s="168">
+        <v>157007.42710199999</v>
+      </c>
+      <c r="G23" s="160">
         <f>F23</f>
-        <v>123035.22673199998</v>
+        <v>157007.42710199999</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -3264,11 +3199,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>158994.79783</v>
-      </c>
-      <c r="G24" s="168">
+        <v>202896.07125499999</v>
+      </c>
+      <c r="G24" s="160">
         <f>F24</f>
-        <v>158994.79783</v>
+        <v>202896.07125499999</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -3316,11 +3251,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>114416.81713</v>
-      </c>
-      <c r="G25" s="168">
+        <v>146009.32230499998</v>
+      </c>
+      <c r="G25" s="160">
         <f t="shared" ref="G25:G26" si="7">F25</f>
-        <v>114416.81713</v>
+        <v>146009.32230499998</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -3366,11 +3301,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>106689.96714200001</v>
-      </c>
-      <c r="G26" s="168">
+        <v>136148.952487</v>
+      </c>
+      <c r="G26" s="160">
         <f t="shared" si="7"/>
-        <v>106689.96714200001</v>
+        <v>136148.952487</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -3402,52 +3337,54 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
-      <c r="A27" s="151">
+      <c r="A27" s="147">
         <v>19</v>
       </c>
-      <c r="B27" s="152" t="s">
+      <c r="B27" s="148" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="153" t="s">
+      <c r="C27" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="153" t="s">
+      <c r="D27" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="154">
+      <c r="E27" s="150">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="155">
-        <v>2054389.0423719024</v>
-      </c>
-      <c r="G27" s="169"/>
-      <c r="H27" s="156">
+      <c r="F27" s="151">
+        <v>2287408.8640416628</v>
+      </c>
+      <c r="G27" s="161">
+        <v>157007.43</v>
+      </c>
+      <c r="H27" s="230">
         <f t="shared" si="0"/>
-        <v>2054389.0423719024</v>
-      </c>
-      <c r="I27" s="157">
+        <v>2130401.4340416626</v>
+      </c>
+      <c r="I27" s="152">
         <f t="shared" si="6"/>
-        <v>76012.394567760392</v>
-      </c>
-      <c r="J27" s="157">
+        <v>78824.853059541521</v>
+      </c>
+      <c r="J27" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="157">
+      <c r="K27" s="152">
         <f t="shared" si="2"/>
         <v>4373.9928</v>
       </c>
-      <c r="L27" s="158">
+      <c r="L27" s="153">
         <f t="shared" si="3"/>
         <v>78113.434301999994</v>
       </c>
-      <c r="M27" s="158">
+      <c r="M27" s="153">
         <f t="shared" si="4"/>
         <v>74520</v>
       </c>
-      <c r="N27" s="158">
+      <c r="N27" s="153">
         <f t="shared" si="5"/>
-        <v>2287408.8640416628</v>
+        <v>2366233.714203204</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -3465,11 +3402,10 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>155038.29301371746</v>
-      </c>
-      <c r="G28" s="168">
-        <f>F28</f>
-        <v>155038.29301371746</v>
+        <v>197243.68925499998</v>
+      </c>
+      <c r="G28" s="160">
+        <v>197250</v>
       </c>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
@@ -3481,7 +3417,7 @@
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.3107450000243261</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="25">
@@ -3494,7 +3430,7 @@
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>197243.68925499998</v>
+        <v>197237.37850999995</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1">
@@ -3512,11 +3448,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>114416.81713</v>
-      </c>
-      <c r="G29" s="168">
+        <v>146009.32230499998</v>
+      </c>
+      <c r="G29" s="160">
         <f>F29</f>
-        <v>114416.81713</v>
+        <v>146009.32230499998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -3565,11 +3501,10 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>106689.96714200001</v>
-      </c>
-      <c r="G30" s="168">
-        <f>F30</f>
-        <v>106689.96714200001</v>
+        <v>136148.952487</v>
+      </c>
+      <c r="G30" s="160">
+        <v>136200</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -3581,7 +3516,7 @@
       </c>
       <c r="J30" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>51.047512999997707</v>
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
@@ -3597,7 +3532,7 @@
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>136148.952487</v>
+        <v>136097.904974</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
@@ -3615,11 +3550,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>123035.22673199998</v>
-      </c>
-      <c r="G31" s="168">
+        <v>157007.42710199999</v>
+      </c>
+      <c r="G31" s="160">
         <f>F31</f>
-        <v>123035.22673199998</v>
+        <v>157007.42710199999</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -3650,7 +3585,7 @@
         <v>157007.42710199999</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15.6">
+    <row r="32" spans="1:15" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -3662,25 +3597,25 @@
         <f>SUM(E9:E31)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="54">
+      <c r="F32" s="100">
         <f>SUM(F9:F31)</f>
-        <v>8286661.5075280182</v>
+        <v>10008287.113094246</v>
       </c>
       <c r="G32" s="100">
-        <f>SUM(G9:G30)</f>
-        <v>2164118.5034630927</v>
-      </c>
-      <c r="H32" s="127">
+        <f>SUM(G9:G31)</f>
+        <v>4651785.9958085511</v>
+      </c>
+      <c r="H32" s="126">
         <f>SUM(H9:H31)</f>
-        <v>5999507.777332928</v>
+        <v>5357493.540791926</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>221981.78776131832</v>
-      </c>
-      <c r="J32" s="101">
+        <v>198227.26100930129</v>
+      </c>
+      <c r="J32" s="100">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>0</v>
+        <v>992.42350623084349</v>
       </c>
       <c r="K32" s="91">
         <f>SUM(K9:K31)</f>
@@ -3696,117 +3631,117 @@
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>10008287.113094246</v>
+        <v>9341525.9262949992</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="188"/>
-      <c r="C34" s="188"/>
-      <c r="D34" s="188"/>
-      <c r="E34" s="188"/>
-      <c r="F34" s="188"/>
-      <c r="G34" s="188"/>
-      <c r="H34" s="188"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="188"/>
-      <c r="K34" s="188"/>
-      <c r="L34" s="188"/>
-      <c r="M34" s="188"/>
-      <c r="N34" s="188"/>
+      <c r="B34" s="170"/>
+      <c r="C34" s="170"/>
+      <c r="D34" s="170"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="170"/>
+      <c r="L34" s="170"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="170"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="188"/>
-      <c r="C35" s="188"/>
-      <c r="D35" s="188"/>
-      <c r="E35" s="188"/>
-      <c r="F35" s="188"/>
-      <c r="G35" s="188"/>
-      <c r="H35" s="188"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="188"/>
-      <c r="K35" s="188"/>
-      <c r="L35" s="188"/>
-      <c r="M35" s="188"/>
-      <c r="N35" s="188"/>
+      <c r="B35" s="170"/>
+      <c r="C35" s="170"/>
+      <c r="D35" s="170"/>
+      <c r="E35" s="170"/>
+      <c r="F35" s="170"/>
+      <c r="G35" s="170"/>
+      <c r="H35" s="170"/>
+      <c r="I35" s="170"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="170"/>
+      <c r="L35" s="170"/>
+      <c r="M35" s="170"/>
+      <c r="N35" s="170"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="188"/>
-      <c r="C36" s="188"/>
-      <c r="D36" s="188"/>
-      <c r="E36" s="188"/>
-      <c r="F36" s="188"/>
-      <c r="G36" s="188"/>
-      <c r="H36" s="188"/>
-      <c r="I36" s="188"/>
-      <c r="J36" s="188"/>
-      <c r="K36" s="188"/>
-      <c r="L36" s="188"/>
-      <c r="M36" s="188"/>
-      <c r="N36" s="188"/>
+      <c r="B36" s="170"/>
+      <c r="C36" s="170"/>
+      <c r="D36" s="170"/>
+      <c r="E36" s="170"/>
+      <c r="F36" s="170"/>
+      <c r="G36" s="170"/>
+      <c r="H36" s="170"/>
+      <c r="I36" s="170"/>
+      <c r="J36" s="170"/>
+      <c r="K36" s="170"/>
+      <c r="L36" s="170"/>
+      <c r="M36" s="170"/>
+      <c r="N36" s="170"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="188"/>
-      <c r="C37" s="188"/>
-      <c r="D37" s="188"/>
-      <c r="E37" s="188"/>
-      <c r="F37" s="188"/>
-      <c r="G37" s="188"/>
-      <c r="H37" s="188"/>
-      <c r="I37" s="188"/>
-      <c r="J37" s="188"/>
-      <c r="K37" s="188"/>
-      <c r="L37" s="188"/>
-      <c r="M37" s="188"/>
-      <c r="N37" s="188"/>
+      <c r="B37" s="170"/>
+      <c r="C37" s="170"/>
+      <c r="D37" s="170"/>
+      <c r="E37" s="170"/>
+      <c r="F37" s="170"/>
+      <c r="G37" s="170"/>
+      <c r="H37" s="170"/>
+      <c r="I37" s="170"/>
+      <c r="J37" s="170"/>
+      <c r="K37" s="170"/>
+      <c r="L37" s="170"/>
+      <c r="M37" s="170"/>
+      <c r="N37" s="170"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="190"/>
-      <c r="B38" s="190"/>
-      <c r="C38" s="190"/>
-      <c r="D38" s="190"/>
-      <c r="E38" s="190"/>
-      <c r="F38" s="190"/>
-      <c r="G38" s="190"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="190"/>
-      <c r="J38" s="190"/>
-      <c r="K38" s="190"/>
-      <c r="L38" s="190"/>
-      <c r="M38" s="190"/>
-      <c r="N38" s="190"/>
+      <c r="A38" s="172"/>
+      <c r="B38" s="172"/>
+      <c r="C38" s="172"/>
+      <c r="D38" s="172"/>
+      <c r="E38" s="172"/>
+      <c r="F38" s="172"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="172"/>
+      <c r="I38" s="172"/>
+      <c r="J38" s="172"/>
+      <c r="K38" s="172"/>
+      <c r="L38" s="172"/>
+      <c r="M38" s="172"/>
+      <c r="N38" s="172"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="190"/>
-      <c r="B39" s="190"/>
-      <c r="C39" s="190"/>
-      <c r="D39" s="190"/>
-      <c r="E39" s="190"/>
-      <c r="F39" s="190"/>
-      <c r="G39" s="190"/>
-      <c r="H39" s="190"/>
-      <c r="I39" s="190"/>
-      <c r="J39" s="190"/>
-      <c r="K39" s="190"/>
-      <c r="L39" s="190"/>
-      <c r="M39" s="190"/>
-      <c r="N39" s="190"/>
+      <c r="A39" s="172"/>
+      <c r="B39" s="172"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="172"/>
+      <c r="E39" s="172"/>
+      <c r="F39" s="172"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="172"/>
+      <c r="I39" s="172"/>
+      <c r="J39" s="172"/>
+      <c r="K39" s="172"/>
+      <c r="L39" s="172"/>
+      <c r="M39" s="172"/>
+      <c r="N39" s="172"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="190"/>
-      <c r="B40" s="190"/>
-      <c r="C40" s="190"/>
-      <c r="D40" s="190"/>
-      <c r="E40" s="190"/>
-      <c r="F40" s="190"/>
-      <c r="G40" s="190"/>
-      <c r="H40" s="190"/>
-      <c r="I40" s="190"/>
-      <c r="J40" s="190"/>
-      <c r="K40" s="190"/>
-      <c r="L40" s="190"/>
-      <c r="M40" s="190"/>
-      <c r="N40" s="190"/>
+      <c r="A40" s="172"/>
+      <c r="B40" s="172"/>
+      <c r="C40" s="172"/>
+      <c r="D40" s="172"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="172"/>
+      <c r="G40" s="172"/>
+      <c r="H40" s="172"/>
+      <c r="I40" s="172"/>
+      <c r="J40" s="172"/>
+      <c r="K40" s="172"/>
+      <c r="L40" s="172"/>
+      <c r="M40" s="172"/>
+      <c r="N40" s="172"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -3827,25 +3762,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="173" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="193"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -3881,13 +3816,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -4248,7 +4183,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -4270,7 +4205,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -4292,7 +4227,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -4314,7 +4249,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -4340,7 +4275,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -4362,7 +4297,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -4384,7 +4319,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -4406,7 +4341,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -4428,7 +4363,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -4468,17 +4403,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K114"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4493,23 +4428,23 @@
     </row>
     <row r="2" spans="1:8" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="228"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="230"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="177"/>
+      <c r="F2" s="177"/>
+      <c r="G2" s="177"/>
+      <c r="H2" s="178"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="202">
+      <c r="E3" s="207">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="203"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="208"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="10"/>
@@ -4545,7 +4480,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -4556,10 +4491,10 @@
         <v>67</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -4588,14 +4523,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:8" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="240"/>
-      <c r="B12" s="195"/>
-      <c r="C12" s="195"/>
-      <c r="D12" s="195"/>
-      <c r="E12" s="195"/>
-      <c r="F12" s="195"/>
-      <c r="G12" s="195"/>
-      <c r="H12" s="241"/>
+      <c r="A12" s="185"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="187"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -4607,626 +4542,625 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:8" ht="15.6">
-      <c r="A14" s="208" t="s">
+    <row r="14" spans="1:8" ht="15.75">
+      <c r="A14" s="211" t="s">
         <v>132</v>
       </c>
-      <c r="B14" s="208"/>
-      <c r="C14" s="208"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="208"/>
-      <c r="F14" s="208"/>
-      <c r="G14" s="208"/>
-      <c r="H14" s="208"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="211"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="170" t="s">
+      <c r="A15" s="215" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
-      <c r="F15" s="171"/>
-      <c r="G15" s="171"/>
-      <c r="H15" s="172">
+      <c r="B15" s="141"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="74">
         <v>194212.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="170" t="s">
+      <c r="A16" s="215" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
-      <c r="F16" s="171"/>
-      <c r="G16" s="171"/>
-      <c r="H16" s="173">
+      <c r="B16" s="141"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="141"/>
+      <c r="H16" s="74">
         <v>23811.3</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A17" s="170" t="s">
+      <c r="A17" s="215" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="171"/>
-      <c r="C17" s="171"/>
-      <c r="D17" s="171"/>
-      <c r="E17" s="171"/>
-      <c r="F17" s="171"/>
-      <c r="G17" s="171"/>
-      <c r="H17" s="173">
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="74">
         <v>33304</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="170" t="s">
+      <c r="A18" s="215" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="171"/>
-      <c r="C18" s="171"/>
-      <c r="D18" s="171"/>
-      <c r="E18" s="171"/>
-      <c r="F18" s="171"/>
-      <c r="G18" s="171"/>
-      <c r="H18" s="173">
+      <c r="B18" s="141"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="141"/>
+      <c r="H18" s="74">
         <v>6666.67</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="170" t="s">
+      <c r="A19" s="215" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="171"/>
-      <c r="C19" s="171"/>
-      <c r="D19" s="171"/>
-      <c r="E19" s="171"/>
-      <c r="F19" s="171"/>
-      <c r="G19" s="171"/>
-      <c r="H19" s="173">
+      <c r="B19" s="141"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="141"/>
+      <c r="H19" s="74">
         <v>-40634.18</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="170" t="s">
+      <c r="A20" s="215" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="171"/>
-      <c r="C20" s="171"/>
-      <c r="D20" s="171"/>
-      <c r="E20" s="171"/>
-      <c r="F20" s="171"/>
-      <c r="G20" s="171"/>
-      <c r="H20" s="173">
+      <c r="B20" s="141"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="74">
         <v>0.41</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="170" t="s">
+      <c r="A21" s="215" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="171"/>
-      <c r="C21" s="171"/>
-      <c r="D21" s="171"/>
-      <c r="E21" s="171"/>
-      <c r="F21" s="171"/>
-      <c r="G21" s="171"/>
-      <c r="H21" s="173">
+      <c r="B21" s="141"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="141"/>
+      <c r="H21" s="74">
         <f>SUM(H15:H20)</f>
         <v>217361</v>
       </c>
       <c r="I21" s="7"/>
     </row>
     <row r="22" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A22" s="234" t="s">
+      <c r="A22" s="216" t="s">
         <v>136</v>
       </c>
-      <c r="B22" s="235"/>
-      <c r="C22" s="235"/>
-      <c r="D22" s="235"/>
-      <c r="E22" s="235"/>
-      <c r="F22" s="235"/>
-      <c r="G22" s="235"/>
-      <c r="H22" s="236"/>
+      <c r="B22" s="216"/>
+      <c r="C22" s="216"/>
+      <c r="D22" s="216"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="216"/>
+      <c r="H22" s="216"/>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="170" t="s">
+      <c r="A23" s="215" t="s">
         <v>136</v>
       </c>
-      <c r="B23" s="171"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="171"/>
-      <c r="H23" s="174"/>
+      <c r="B23" s="141"/>
+      <c r="C23" s="141"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="141"/>
+      <c r="H23" s="74"/>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="170"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
-      <c r="H24" s="174">
+      <c r="A24" s="215"/>
+      <c r="B24" s="141"/>
+      <c r="C24" s="141"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="141"/>
+      <c r="H24" s="74">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="170"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="171"/>
-      <c r="H25" s="174">
+      <c r="A25" s="215"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="74">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="170"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="174">
+      <c r="A26" s="215"/>
+      <c r="B26" s="141"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="74">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" hidden="1">
-      <c r="A27" s="170" t="s">
+      <c r="A27" s="215" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="171"/>
-      <c r="C27" s="171"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="171"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="174"/>
+      <c r="B27" s="141"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="74"/>
     </row>
     <row r="28" spans="1:9" hidden="1">
-      <c r="A28" s="170" t="s">
+      <c r="A28" s="215" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="171"/>
-      <c r="C28" s="171"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="174"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="74"/>
     </row>
     <row r="29" spans="1:9" hidden="1">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="215" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="171"/>
-      <c r="H29" s="175">
+      <c r="B29" s="141"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="70">
         <f>SUM(H23:H28)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="231" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="232"/>
-      <c r="C30" s="232"/>
-      <c r="D30" s="232"/>
-      <c r="E30" s="232"/>
-      <c r="F30" s="232"/>
-      <c r="G30" s="232"/>
-      <c r="H30" s="233"/>
+      <c r="A30" s="217" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
+      <c r="D30" s="217"/>
+      <c r="E30" s="217"/>
+      <c r="F30" s="217"/>
+      <c r="G30" s="217"/>
+      <c r="H30" s="217"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="79" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
+      <c r="A31" s="141" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="141"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="141"/>
       <c r="H31" s="74">
         <v>32000</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="79"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="80"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="80"/>
-      <c r="G32" s="80"/>
+      <c r="A32" s="141"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
       <c r="H32" s="74"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
+      <c r="B33" s="141"/>
+      <c r="C33" s="141"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="141"/>
       <c r="H33" s="74">
         <f>SUM(H31:H32)</f>
         <v>32000</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A34" s="209" t="s">
+      <c r="A34" s="218" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="210"/>
-      <c r="C34" s="210"/>
-      <c r="D34" s="210"/>
-      <c r="E34" s="210"/>
-      <c r="F34" s="210"/>
-      <c r="G34" s="210"/>
-      <c r="H34" s="211"/>
+      <c r="B34" s="218"/>
+      <c r="C34" s="218"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="218"/>
     </row>
     <row r="35" spans="1:8" hidden="1">
-      <c r="A35" s="170"/>
-      <c r="B35" s="171"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="171"/>
-      <c r="H35" s="173"/>
+      <c r="A35" s="215"/>
+      <c r="B35" s="141"/>
+      <c r="C35" s="141"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="141"/>
+      <c r="H35" s="74"/>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="170" t="s">
+      <c r="A36" s="215" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="176"/>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
-      <c r="H36" s="242">
+      <c r="B36" s="219"/>
+      <c r="C36" s="141"/>
+      <c r="D36" s="141"/>
+      <c r="E36" s="141"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="141"/>
+      <c r="H36" s="74">
         <f>28769.66+1289.97+11609.77</f>
         <v>41669.4</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="79" t="s">
+      <c r="A37" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="80"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="80"/>
-      <c r="G37" s="80"/>
-      <c r="H37" s="126">
+      <c r="B37" s="141"/>
+      <c r="C37" s="141"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="141"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
+      <c r="H37" s="74">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="141" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="80"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="80"/>
-      <c r="G38" s="80"/>
+      <c r="B38" s="141"/>
+      <c r="C38" s="141"/>
+      <c r="D38" s="141"/>
+      <c r="E38" s="141"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="141"/>
       <c r="H38" s="74">
         <f>SUM(H35:H37)</f>
         <v>41669.4</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="209" t="s">
+      <c r="A39" s="218" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="218"/>
+      <c r="C39" s="218"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="218"/>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A40" s="141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" s="141"/>
+      <c r="C40" s="141"/>
+      <c r="D40" s="141"/>
+      <c r="E40" s="141"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="141"/>
+      <c r="H40" s="74">
+        <v>937121.46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="220" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="141"/>
+      <c r="C41" s="141"/>
+      <c r="D41" s="141"/>
+      <c r="E41" s="141"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="141"/>
+      <c r="H41" s="74">
+        <v>75376.820000000007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="141" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="141"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="145">
+        <f>SUM(H40:H41)</f>
+        <v>1012498.28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="211" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="211"/>
+      <c r="C43" s="211"/>
+      <c r="D43" s="211"/>
+      <c r="E43" s="211"/>
+      <c r="F43" s="211"/>
+      <c r="G43" s="211"/>
+      <c r="H43" s="211"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="81" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="141"/>
+      <c r="C44" s="141"/>
+      <c r="D44" s="141"/>
+      <c r="E44" s="141"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="141"/>
+      <c r="H44" s="74">
+        <v>47700</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="141" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="141"/>
+      <c r="C45" s="141"/>
+      <c r="D45" s="141"/>
+      <c r="E45" s="141"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="141"/>
+      <c r="H45" s="74">
+        <v>18611.07</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="141" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="141"/>
+      <c r="C46" s="141"/>
+      <c r="D46" s="141"/>
+      <c r="E46" s="141"/>
+      <c r="F46" s="141"/>
+      <c r="G46" s="141"/>
+      <c r="H46" s="74">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="141" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" s="141"/>
+      <c r="C47" s="141"/>
+      <c r="D47" s="141"/>
+      <c r="E47" s="141"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="141"/>
+      <c r="H47" s="74">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="141" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" s="141"/>
+      <c r="C48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
+      <c r="F48" s="141"/>
+      <c r="G48" s="141"/>
+      <c r="H48" s="74">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="141" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="141"/>
+      <c r="C49" s="141"/>
+      <c r="D49" s="141"/>
+      <c r="E49" s="141"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="141"/>
+      <c r="H49" s="74">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="141" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" s="141"/>
+      <c r="C50" s="141"/>
+      <c r="D50" s="141"/>
+      <c r="E50" s="141"/>
+      <c r="F50" s="141"/>
+      <c r="G50" s="141"/>
+      <c r="H50" s="70">
+        <f>SUM(H44:H49)</f>
+        <v>796311.07000000007</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="211" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="211"/>
+      <c r="C51" s="211"/>
+      <c r="D51" s="211"/>
+      <c r="E51" s="211"/>
+      <c r="F51" s="211"/>
+      <c r="G51" s="211"/>
+      <c r="H51" s="211"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="141" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="141"/>
+      <c r="C52" s="141"/>
+      <c r="D52" s="141"/>
+      <c r="E52" s="141"/>
+      <c r="F52" s="141"/>
+      <c r="G52" s="141"/>
+      <c r="H52" s="74">
+        <v>139785.35999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="141" t="s">
+        <v>125</v>
+      </c>
+      <c r="B53" s="141"/>
+      <c r="C53" s="141"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="F53" s="141"/>
+      <c r="G53" s="141"/>
+      <c r="H53" s="74">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="141"/>
+      <c r="B54" s="141"/>
+      <c r="C54" s="141"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="141"/>
+      <c r="F54" s="141"/>
+      <c r="G54" s="141"/>
+      <c r="H54" s="74"/>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="141" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="141"/>
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="141"/>
+      <c r="F55" s="141"/>
+      <c r="G55" s="141"/>
+      <c r="H55" s="221">
+        <f>SUM(H52:H54)</f>
+        <v>167785.36</v>
+      </c>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="212" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="210"/>
-      <c r="C39" s="210"/>
-      <c r="D39" s="210"/>
-      <c r="E39" s="210"/>
-      <c r="F39" s="210"/>
-      <c r="G39" s="210"/>
-      <c r="H39" s="211"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A40" s="177" t="s">
+      <c r="B56" s="213"/>
+      <c r="C56" s="213"/>
+      <c r="D56" s="213"/>
+      <c r="E56" s="213"/>
+      <c r="F56" s="213"/>
+      <c r="G56" s="213"/>
+      <c r="H56" s="214"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1">
+      <c r="A57" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="70">
+        <v>20546.41</v>
+      </c>
+      <c r="I57" s="60"/>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1">
+      <c r="A58" s="81" t="s">
+        <v>77</v>
+      </c>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="70">
+        <f>SUM(H57)</f>
+        <v>20546.41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1">
+      <c r="A59" s="211" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="171"/>
-      <c r="C40" s="171"/>
-      <c r="D40" s="171"/>
-      <c r="E40" s="171"/>
-      <c r="F40" s="171"/>
-      <c r="G40" s="171"/>
-      <c r="H40" s="242">
-        <v>937121.46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A41" s="177" t="s">
-        <v>149</v>
-      </c>
-      <c r="B41" s="171"/>
-      <c r="C41" s="171"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="171"/>
-      <c r="H41" s="173">
-        <v>435480.04</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A42" s="177" t="s">
-        <v>150</v>
-      </c>
-      <c r="B42" s="171"/>
-      <c r="C42" s="171"/>
-      <c r="D42" s="171"/>
-      <c r="E42" s="171"/>
-      <c r="F42" s="171"/>
-      <c r="G42" s="171"/>
-      <c r="H42" s="173"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="178" t="s">
-        <v>106</v>
-      </c>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
-      <c r="D43" s="171"/>
-      <c r="E43" s="171"/>
-      <c r="F43" s="171"/>
-      <c r="G43" s="171"/>
-      <c r="H43" s="242">
-        <v>75376.820000000007</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
-      <c r="A44" s="177" t="s">
-        <v>77</v>
-      </c>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
-      <c r="D44" s="171"/>
-      <c r="E44" s="171"/>
-      <c r="F44" s="171"/>
-      <c r="G44" s="171"/>
-      <c r="H44" s="69">
-        <f>SUM(H40:H43)</f>
-        <v>1447978.32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="208" t="s">
-        <v>147</v>
-      </c>
-      <c r="B45" s="208"/>
-      <c r="C45" s="208"/>
-      <c r="D45" s="208"/>
-      <c r="E45" s="208"/>
-      <c r="F45" s="208"/>
-      <c r="G45" s="208"/>
-      <c r="H45" s="208"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="179" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="171"/>
-      <c r="C46" s="171"/>
-      <c r="D46" s="171"/>
-      <c r="E46" s="171"/>
-      <c r="F46" s="171"/>
-      <c r="G46" s="171"/>
-      <c r="H46" s="74">
-        <v>47700</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="177" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="171"/>
-      <c r="C47" s="171"/>
-      <c r="D47" s="171"/>
-      <c r="E47" s="171"/>
-      <c r="F47" s="171"/>
-      <c r="G47" s="171"/>
-      <c r="H47" s="243">
-        <v>18611.07</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="177" t="s">
-        <v>160</v>
-      </c>
-      <c r="B48" s="171"/>
-      <c r="C48" s="171"/>
-      <c r="D48" s="171"/>
-      <c r="E48" s="171"/>
-      <c r="F48" s="171"/>
-      <c r="G48" s="171"/>
-      <c r="H48" s="74">
-        <v>85000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="177" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="171"/>
-      <c r="C49" s="171"/>
-      <c r="D49" s="171"/>
-      <c r="E49" s="171"/>
-      <c r="F49" s="171"/>
-      <c r="G49" s="171"/>
-      <c r="H49" s="243">
-        <v>165000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="245" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="171"/>
-      <c r="C50" s="171"/>
-      <c r="D50" s="171"/>
-      <c r="E50" s="171"/>
-      <c r="F50" s="171"/>
-      <c r="G50" s="171"/>
-      <c r="H50" s="243">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="177" t="s">
-        <v>140</v>
-      </c>
-      <c r="B51" s="171"/>
-      <c r="C51" s="171"/>
-      <c r="D51" s="171"/>
-      <c r="E51" s="171"/>
-      <c r="F51" s="171"/>
-      <c r="G51" s="171"/>
-      <c r="H51" s="74"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="177" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="171"/>
-      <c r="C52" s="171"/>
-      <c r="D52" s="171"/>
-      <c r="E52" s="171"/>
-      <c r="F52" s="171"/>
-      <c r="G52" s="171"/>
-      <c r="H52" s="70">
-        <f>SUM(H46:H51)</f>
-        <v>416311.07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="212" t="s">
-        <v>148</v>
-      </c>
-      <c r="B53" s="213"/>
-      <c r="C53" s="213"/>
-      <c r="D53" s="213"/>
-      <c r="E53" s="213"/>
-      <c r="F53" s="213"/>
-      <c r="G53" s="213"/>
-      <c r="H53" s="214"/>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="177" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" s="171"/>
-      <c r="C54" s="171"/>
-      <c r="D54" s="171"/>
-      <c r="E54" s="171"/>
-      <c r="F54" s="171"/>
-      <c r="G54" s="171"/>
-      <c r="H54" s="172">
-        <v>139785.35999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="177" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="171"/>
-      <c r="C55" s="171"/>
-      <c r="D55" s="171"/>
-      <c r="E55" s="171"/>
-      <c r="F55" s="171"/>
-      <c r="G55" s="171"/>
-      <c r="H55" s="173">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="177" t="s">
-        <v>142</v>
-      </c>
-      <c r="B56" s="171"/>
-      <c r="C56" s="171"/>
-      <c r="D56" s="171"/>
-      <c r="E56" s="171"/>
-      <c r="F56" s="171"/>
-      <c r="G56" s="171"/>
-      <c r="H56" s="173">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="171" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="171"/>
-      <c r="C57" s="171"/>
-      <c r="D57" s="171"/>
-      <c r="E57" s="171"/>
-      <c r="F57" s="171"/>
-      <c r="G57" s="171"/>
-      <c r="H57" s="69">
-        <f>SUM(H54:H56)</f>
-        <v>170785.36</v>
-      </c>
-      <c r="K57" s="7"/>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="212" t="s">
-        <v>151</v>
-      </c>
-      <c r="B58" s="213"/>
-      <c r="C58" s="213"/>
-      <c r="D58" s="213"/>
-      <c r="E58" s="213"/>
-      <c r="F58" s="213"/>
-      <c r="G58" s="213"/>
-      <c r="H58" s="214"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="81" t="s">
-        <v>127</v>
-      </c>
-      <c r="B59" s="81"/>
-      <c r="C59" s="81"/>
-      <c r="D59" s="81"/>
-      <c r="E59" s="81"/>
-      <c r="F59" s="81"/>
-      <c r="G59" s="81"/>
-      <c r="H59" s="244">
-        <v>20546.41</v>
-      </c>
-      <c r="I59" s="60"/>
+      <c r="B59" s="211"/>
+      <c r="C59" s="211"/>
+      <c r="D59" s="211"/>
+      <c r="E59" s="211"/>
+      <c r="F59" s="211"/>
+      <c r="G59" s="211"/>
+      <c r="H59" s="211"/>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
       <c r="A60" s="81" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="B60" s="81"/>
       <c r="C60" s="81"/>
@@ -5235,26 +5169,21 @@
       <c r="F60" s="81"/>
       <c r="G60" s="81"/>
       <c r="H60" s="70">
-        <f>SUM(H59)</f>
-        <v>20546.41</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1">
-      <c r="A61" s="208" t="s">
-        <v>152</v>
-      </c>
-      <c r="B61" s="208"/>
-      <c r="C61" s="208"/>
-      <c r="D61" s="208"/>
-      <c r="E61" s="208"/>
-      <c r="F61" s="208"/>
-      <c r="G61" s="208"/>
-      <c r="H61" s="208"/>
+      <c r="A61" s="81"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="81"/>
+      <c r="F61" s="81"/>
+      <c r="G61" s="81"/>
+      <c r="H61" s="70"/>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1">
-      <c r="A62" s="81" t="s">
-        <v>144</v>
-      </c>
+      <c r="A62" s="81"/>
       <c r="B62" s="81"/>
       <c r="C62" s="81"/>
       <c r="D62" s="81"/>
@@ -5262,660 +5191,604 @@
       <c r="F62" s="81"/>
       <c r="G62" s="81"/>
       <c r="H62" s="70">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1">
-      <c r="A63" s="81"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A63" s="81" t="s">
+        <v>78</v>
+      </c>
       <c r="B63" s="81"/>
       <c r="C63" s="81"/>
       <c r="D63" s="81"/>
       <c r="E63" s="81"/>
       <c r="F63" s="81"/>
       <c r="G63" s="81"/>
-      <c r="H63" s="70"/>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1">
-      <c r="A64" s="81"/>
-      <c r="B64" s="81"/>
-      <c r="C64" s="81"/>
-      <c r="D64" s="81"/>
-      <c r="E64" s="81"/>
-      <c r="F64" s="81"/>
-      <c r="G64" s="81"/>
-      <c r="H64" s="70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A65" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="B65" s="81"/>
-      <c r="C65" s="81"/>
-      <c r="D65" s="81"/>
-      <c r="E65" s="81"/>
-      <c r="F65" s="81"/>
-      <c r="G65" s="81"/>
-      <c r="H65" s="70">
-        <f>SUM(H62:H64)</f>
+      <c r="H63" s="70">
+        <f>SUM(H60:H62)</f>
         <v>100000</v>
       </c>
-      <c r="I65" s="60"/>
-    </row>
-    <row r="66" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="212"/>
-      <c r="B66" s="213"/>
-      <c r="C66" s="213"/>
-      <c r="D66" s="213"/>
-      <c r="E66" s="213"/>
-      <c r="F66" s="213"/>
-      <c r="G66" s="213"/>
-      <c r="H66" s="214"/>
-    </row>
-    <row r="67" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A67" s="82"/>
-      <c r="B67" s="83"/>
-      <c r="C67" s="83"/>
-      <c r="D67" s="83"/>
-      <c r="E67" s="83"/>
-      <c r="F67" s="83"/>
-      <c r="G67" s="83"/>
-      <c r="H67" s="180">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A68" s="181"/>
-      <c r="B68" s="182"/>
-      <c r="C68" s="182"/>
-      <c r="D68" s="182"/>
-      <c r="E68" s="182"/>
-      <c r="F68" s="182"/>
-      <c r="G68" s="182"/>
-      <c r="H68" s="183">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A69" s="184"/>
-      <c r="B69" s="185"/>
-      <c r="C69" s="185"/>
-      <c r="D69" s="185"/>
-      <c r="E69" s="185"/>
-      <c r="F69" s="185"/>
-      <c r="G69" s="185"/>
-      <c r="H69" s="180">
-        <f>H67+H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A70" s="223" t="s">
+      <c r="I63" s="60"/>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="212"/>
+      <c r="B64" s="213"/>
+      <c r="C64" s="213"/>
+      <c r="D64" s="213"/>
+      <c r="E64" s="213"/>
+      <c r="F64" s="213"/>
+      <c r="G64" s="213"/>
+      <c r="H64" s="214"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A65" s="82"/>
+      <c r="B65" s="83"/>
+      <c r="C65" s="83"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="83"/>
+      <c r="G65" s="83"/>
+      <c r="H65" s="162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A66" s="163"/>
+      <c r="B66" s="164"/>
+      <c r="C66" s="164"/>
+      <c r="D66" s="164"/>
+      <c r="E66" s="164"/>
+      <c r="F66" s="164"/>
+      <c r="G66" s="164"/>
+      <c r="H66" s="165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A67" s="166"/>
+      <c r="B67" s="167"/>
+      <c r="C67" s="167"/>
+      <c r="D67" s="167"/>
+      <c r="E67" s="167"/>
+      <c r="F67" s="167"/>
+      <c r="G67" s="167"/>
+      <c r="H67" s="162">
+        <f>H65+H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A68" s="193" t="s">
         <v>86</v>
       </c>
-      <c r="B70" s="224"/>
-      <c r="C70" s="224"/>
-      <c r="D70" s="224"/>
-      <c r="E70" s="224"/>
-      <c r="F70" s="224"/>
-      <c r="G70" s="224"/>
-      <c r="H70" s="186">
-        <f>H65</f>
+      <c r="B68" s="194"/>
+      <c r="C68" s="194"/>
+      <c r="D68" s="194"/>
+      <c r="E68" s="194"/>
+      <c r="F68" s="194"/>
+      <c r="G68" s="194"/>
+      <c r="H68" s="168">
+        <f>H63</f>
         <v>100000</v>
       </c>
     </row>
-    <row r="71" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A71" s="226"/>
-      <c r="B71" s="226"/>
-      <c r="C71" s="226"/>
-      <c r="D71" s="226"/>
-      <c r="E71" s="226"/>
-      <c r="F71" s="226"/>
-      <c r="G71" s="226"/>
-      <c r="H71" s="226"/>
-    </row>
-    <row r="72" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A72" s="227"/>
-      <c r="B72" s="227"/>
-      <c r="C72" s="227"/>
-      <c r="D72" s="227"/>
-      <c r="E72" s="227"/>
-      <c r="F72" s="227"/>
-      <c r="G72" s="227"/>
-      <c r="H72" s="227"/>
-    </row>
-    <row r="73" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A73" s="225" t="s">
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A69" s="198"/>
+      <c r="B69" s="198"/>
+      <c r="C69" s="198"/>
+      <c r="D69" s="198"/>
+      <c r="E69" s="198"/>
+      <c r="F69" s="198"/>
+      <c r="G69" s="198"/>
+      <c r="H69" s="198"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A70" s="199"/>
+      <c r="B70" s="199"/>
+      <c r="C70" s="199"/>
+      <c r="D70" s="199"/>
+      <c r="E70" s="199"/>
+      <c r="F70" s="199"/>
+      <c r="G70" s="199"/>
+      <c r="H70" s="199"/>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A71" s="197" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="225"/>
-      <c r="C73" s="225"/>
-      <c r="D73" s="225"/>
-      <c r="E73" s="225"/>
-      <c r="F73" s="225"/>
-      <c r="G73" s="225"/>
-      <c r="H73" s="187"/>
-    </row>
-    <row r="74" spans="1:9" s="6" customFormat="1">
-      <c r="A74" s="237"/>
-      <c r="B74" s="238"/>
-      <c r="C74" s="238"/>
-      <c r="D74" s="238"/>
-      <c r="E74" s="238"/>
-      <c r="F74" s="238"/>
-      <c r="G74" s="239"/>
-      <c r="H74" s="74"/>
-    </row>
-    <row r="75" spans="1:9" s="6" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A75" s="237"/>
-      <c r="B75" s="238"/>
-      <c r="C75" s="238"/>
-      <c r="D75" s="238"/>
-      <c r="E75" s="238"/>
-      <c r="F75" s="238"/>
-      <c r="G75" s="239"/>
-      <c r="H75" s="74"/>
-    </row>
-    <row r="76" spans="1:9" s="6" customFormat="1" ht="14.1" customHeight="1">
-      <c r="A76" s="132"/>
-      <c r="B76" s="133"/>
-      <c r="C76" s="133"/>
-      <c r="D76" s="133"/>
-      <c r="E76" s="133"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="134"/>
-      <c r="H76" s="74"/>
-    </row>
-    <row r="77" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A77" s="135" t="s">
+      <c r="B71" s="197"/>
+      <c r="C71" s="197"/>
+      <c r="D71" s="197"/>
+      <c r="E71" s="197"/>
+      <c r="F71" s="197"/>
+      <c r="G71" s="197"/>
+      <c r="H71" s="169"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A72" s="182" t="s">
+        <v>159</v>
+      </c>
+      <c r="B72" s="183"/>
+      <c r="C72" s="183"/>
+      <c r="D72" s="183"/>
+      <c r="E72" s="183"/>
+      <c r="F72" s="183"/>
+      <c r="G72" s="184"/>
+      <c r="H72" s="74">
+        <f>19000+81000</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A73" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="B77" s="81"/>
-      <c r="C77" s="81"/>
-      <c r="D77" s="81"/>
-      <c r="E77" s="81"/>
-      <c r="F77" s="81"/>
-      <c r="G77" s="81"/>
-      <c r="H77" s="70">
-        <f>SUM(H74:H76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A78" s="136"/>
-      <c r="B78" s="136"/>
-      <c r="C78" s="136"/>
-      <c r="D78" s="136"/>
-      <c r="E78" s="136"/>
-      <c r="F78" s="136"/>
-      <c r="G78" s="136"/>
-      <c r="H78" s="137"/>
-    </row>
-    <row r="79" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A79" s="204" t="s">
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="81"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="70">
+        <f>SUM(H72:H72)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A74" s="132"/>
+      <c r="B74" s="132"/>
+      <c r="C74" s="132"/>
+      <c r="D74" s="132"/>
+      <c r="E74" s="132"/>
+      <c r="F74" s="132"/>
+      <c r="G74" s="132"/>
+      <c r="H74" s="133"/>
+    </row>
+    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A75" s="195" t="s">
         <v>87</v>
       </c>
-      <c r="B79" s="205"/>
-      <c r="C79" s="205"/>
-      <c r="D79" s="205"/>
-      <c r="E79" s="205"/>
-      <c r="F79" s="205"/>
-      <c r="G79" s="205"/>
-      <c r="H79" s="138">
-        <f>H77</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A80" s="218" t="s">
+      <c r="B75" s="196"/>
+      <c r="C75" s="196"/>
+      <c r="D75" s="196"/>
+      <c r="E75" s="196"/>
+      <c r="F75" s="196"/>
+      <c r="G75" s="196"/>
+      <c r="H75" s="134">
+        <f>H73</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A76" s="179" t="s">
         <v>95</v>
       </c>
-      <c r="B80" s="219"/>
-      <c r="C80" s="219"/>
-      <c r="D80" s="219"/>
-      <c r="E80" s="219"/>
-      <c r="F80" s="219"/>
-      <c r="G80" s="220"/>
-      <c r="H80" s="138"/>
-    </row>
-    <row r="81" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A81" s="218" t="s">
+      <c r="B76" s="180"/>
+      <c r="C76" s="180"/>
+      <c r="D76" s="180"/>
+      <c r="E76" s="180"/>
+      <c r="F76" s="180"/>
+      <c r="G76" s="181"/>
+      <c r="H76" s="134"/>
+    </row>
+    <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A77" s="179" t="s">
         <v>100</v>
       </c>
-      <c r="B81" s="219"/>
-      <c r="C81" s="219"/>
-      <c r="D81" s="219"/>
-      <c r="E81" s="219"/>
-      <c r="F81" s="219"/>
-      <c r="G81" s="220"/>
-      <c r="H81" s="138">
+      <c r="B77" s="180"/>
+      <c r="C77" s="180"/>
+      <c r="D77" s="180"/>
+      <c r="E77" s="180"/>
+      <c r="F77" s="180"/>
+      <c r="G77" s="181"/>
+      <c r="H77" s="134">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="195" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="196"/>
+      <c r="C78" s="196"/>
+      <c r="D78" s="196"/>
+      <c r="E78" s="196"/>
+      <c r="F78" s="196"/>
+      <c r="G78" s="196"/>
+      <c r="H78" s="134">
+        <f>H33+H42+H50+H55+H58+H38+H21+H29</f>
+        <v>2288171.5199999996</v>
+      </c>
+      <c r="J78" s="7"/>
+      <c r="K78" s="146"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75">
+      <c r="A79" s="188" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" s="189"/>
+      <c r="C79" s="189"/>
+      <c r="D79" s="189"/>
+      <c r="E79" s="189"/>
+      <c r="F79" s="189"/>
+      <c r="G79" s="190"/>
+      <c r="H79" s="135">
+        <f>H76+H78</f>
+        <v>2288171.5199999996</v>
+      </c>
+      <c r="I79" s="130"/>
+      <c r="J79" s="200"/>
+      <c r="K79" s="200"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75">
+      <c r="A80" s="188" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="189"/>
+      <c r="C80" s="189"/>
+      <c r="D80" s="189"/>
+      <c r="E80" s="189"/>
+      <c r="F80" s="189"/>
+      <c r="G80" s="190"/>
+      <c r="H80" s="136">
+        <f>H77+H75</f>
         <v>1800000</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="18">
-      <c r="A82" s="204" t="s">
-        <v>96</v>
-      </c>
-      <c r="B82" s="205"/>
-      <c r="C82" s="205"/>
-      <c r="D82" s="205"/>
-      <c r="E82" s="205"/>
-      <c r="F82" s="205"/>
-      <c r="G82" s="205"/>
+    <row r="81" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A81" s="191" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="192"/>
+      <c r="C81" s="192"/>
+      <c r="D81" s="192"/>
+      <c r="E81" s="192"/>
+      <c r="F81" s="192"/>
+      <c r="G81" s="192"/>
+      <c r="H81" s="137">
+        <f>H78+H75</f>
+        <v>2388171.5199999996</v>
+      </c>
+      <c r="J81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" hidden="1">
+      <c r="A82" s="209" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" s="210"/>
+      <c r="C82" s="210"/>
+      <c r="D82" s="210"/>
+      <c r="E82" s="210"/>
+      <c r="F82" s="210"/>
+      <c r="G82" s="210"/>
       <c r="H82" s="138">
-        <f>H33+H44+H52+H57+H60+H38+H21+H29</f>
-        <v>2346651.56</v>
+        <f>H67</f>
+        <v>0</v>
       </c>
       <c r="J82" s="7"/>
-      <c r="K82" s="150"/>
-    </row>
-    <row r="83" spans="1:11" ht="18">
-      <c r="A83" s="215" t="s">
-        <v>130</v>
-      </c>
-      <c r="B83" s="216"/>
-      <c r="C83" s="216"/>
-      <c r="D83" s="216"/>
-      <c r="E83" s="216"/>
-      <c r="F83" s="216"/>
-      <c r="G83" s="217"/>
-      <c r="H83" s="139">
-        <f>H80+H82</f>
-        <v>2346651.56</v>
-      </c>
-      <c r="I83" s="131"/>
-      <c r="J83" s="194"/>
-      <c r="K83" s="194"/>
-    </row>
-    <row r="84" spans="1:11" ht="18">
-      <c r="A84" s="215" t="s">
-        <v>101</v>
-      </c>
-      <c r="B84" s="216"/>
-      <c r="C84" s="216"/>
-      <c r="D84" s="216"/>
-      <c r="E84" s="216"/>
-      <c r="F84" s="216"/>
-      <c r="G84" s="217"/>
-      <c r="H84" s="140">
-        <f>H81+H79</f>
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A85" s="221" t="s">
-        <v>89</v>
-      </c>
-      <c r="B85" s="222"/>
-      <c r="C85" s="222"/>
-      <c r="D85" s="222"/>
-      <c r="E85" s="222"/>
-      <c r="F85" s="222"/>
-      <c r="G85" s="222"/>
-      <c r="H85" s="141">
-        <f>H82+H79</f>
-        <v>2346651.56</v>
-      </c>
+    </row>
+    <row r="83" spans="1:11" ht="18.75" hidden="1">
+      <c r="A83" s="139"/>
+      <c r="B83" s="139"/>
+      <c r="C83" s="139"/>
+      <c r="D83" s="139"/>
+      <c r="E83" s="139"/>
+      <c r="F83" s="139"/>
+      <c r="G83" s="139"/>
+      <c r="H83" s="140"/>
+      <c r="J83" s="7"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75" hidden="1">
+      <c r="A84" s="139"/>
+      <c r="B84" s="139"/>
+      <c r="C84" s="139"/>
+      <c r="D84" s="139"/>
+      <c r="E84" s="139"/>
+      <c r="F84" s="139"/>
+      <c r="G84" s="139"/>
+      <c r="H84" s="140"/>
+      <c r="J84" s="7"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75" hidden="1">
+      <c r="A85" s="139"/>
+      <c r="B85" s="139"/>
+      <c r="C85" s="139"/>
+      <c r="D85" s="139"/>
+      <c r="E85" s="139"/>
+      <c r="F85" s="139"/>
+      <c r="G85" s="139"/>
+      <c r="H85" s="140"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:11" ht="18" hidden="1">
-      <c r="A86" s="206" t="s">
-        <v>17</v>
-      </c>
-      <c r="B86" s="207"/>
-      <c r="C86" s="207"/>
-      <c r="D86" s="207"/>
-      <c r="E86" s="207"/>
-      <c r="F86" s="207"/>
-      <c r="G86" s="207"/>
-      <c r="H86" s="142">
-        <f>H69</f>
-        <v>0</v>
-      </c>
-      <c r="J86" s="7"/>
-    </row>
-    <row r="87" spans="1:11" ht="18" hidden="1">
-      <c r="A87" s="143"/>
-      <c r="B87" s="143"/>
-      <c r="C87" s="143"/>
-      <c r="D87" s="143"/>
-      <c r="E87" s="143"/>
-      <c r="F87" s="143"/>
-      <c r="G87" s="143"/>
-      <c r="H87" s="144"/>
-      <c r="J87" s="7"/>
-    </row>
-    <row r="88" spans="1:11" ht="18" hidden="1">
-      <c r="A88" s="143"/>
+    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A86" s="141"/>
+      <c r="B86" s="141"/>
+      <c r="C86" s="141"/>
+      <c r="D86" s="141"/>
+      <c r="E86" s="141"/>
+      <c r="F86" s="141"/>
+      <c r="G86" s="141"/>
+      <c r="H86" s="141"/>
+    </row>
+    <row r="87" spans="1:11" ht="18.75">
+      <c r="A87" s="204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" s="205"/>
+      <c r="C87" s="205"/>
+      <c r="D87" s="205"/>
+      <c r="E87" s="205"/>
+      <c r="F87" s="205"/>
+      <c r="G87" s="205"/>
+      <c r="H87" s="206"/>
+    </row>
+    <row r="88" spans="1:11" ht="18.75">
+      <c r="A88" s="142" t="s">
+        <v>12</v>
+      </c>
       <c r="B88" s="143"/>
       <c r="C88" s="143"/>
       <c r="D88" s="143"/>
       <c r="E88" s="143"/>
       <c r="F88" s="143"/>
       <c r="G88" s="143"/>
-      <c r="H88" s="144"/>
-      <c r="J88" s="7"/>
-    </row>
-    <row r="89" spans="1:11" ht="18" hidden="1">
-      <c r="A89" s="143"/>
-      <c r="B89" s="143"/>
-      <c r="C89" s="143"/>
-      <c r="D89" s="143"/>
-      <c r="E89" s="143"/>
-      <c r="F89" s="143"/>
-      <c r="G89" s="143"/>
-      <c r="H89" s="144"/>
-      <c r="J89" s="7"/>
-    </row>
-    <row r="90" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A90" s="145"/>
-      <c r="B90" s="145"/>
-      <c r="C90" s="145"/>
-      <c r="D90" s="145"/>
-      <c r="E90" s="145"/>
-      <c r="F90" s="145"/>
-      <c r="G90" s="145"/>
-      <c r="H90" s="145"/>
-    </row>
-    <row r="91" spans="1:11" ht="18">
-      <c r="A91" s="199" t="s">
-        <v>10</v>
-      </c>
-      <c r="B91" s="200"/>
-      <c r="C91" s="200"/>
-      <c r="D91" s="200"/>
-      <c r="E91" s="200"/>
-      <c r="F91" s="200"/>
-      <c r="G91" s="200"/>
-      <c r="H91" s="201"/>
-    </row>
-    <row r="92" spans="1:11" ht="18">
-      <c r="A92" s="146" t="s">
+      <c r="H88" s="144">
+        <v>839961.22447473579</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="82" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" s="83"/>
+      <c r="C89" s="83"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
+      <c r="F89" s="83"/>
+      <c r="G89" s="83"/>
+      <c r="H89" s="145">
+        <f>Planilla!G32</f>
+        <v>4651785.9958085511</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" s="80"/>
+      <c r="C90" s="80"/>
+      <c r="D90" s="80"/>
+      <c r="E90" s="80"/>
+      <c r="F90" s="80"/>
+      <c r="G90" s="80"/>
+      <c r="H90" s="69">
+        <f>-(H81)</f>
+        <v>-2388171.5199999996</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" s="80"/>
+      <c r="C91" s="80"/>
+      <c r="D91" s="80"/>
+      <c r="E91" s="80"/>
+      <c r="F91" s="80"/>
+      <c r="G91" s="80"/>
+      <c r="H91" s="69">
+        <f>-H68</f>
+        <v>-100000</v>
+      </c>
+      <c r="K91" s="229" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="79" t="s">
+        <v>75</v>
+      </c>
+      <c r="B92" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="C92" s="80"/>
+      <c r="D92" s="80"/>
+      <c r="E92" s="80"/>
+      <c r="F92" s="80"/>
+      <c r="G92" s="80"/>
+      <c r="H92" s="125">
+        <v>115393.04</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B93" s="80"/>
+      <c r="C93" s="80"/>
+      <c r="D93" s="80"/>
+      <c r="E93" s="80"/>
+      <c r="F93" s="80"/>
+      <c r="G93" s="80"/>
+      <c r="H93" s="125">
+        <v>36320.800000000003</v>
+      </c>
+      <c r="I93" s="146"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B94" s="84"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="18.75">
+      <c r="A95" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="85">
+        <f>SUM(H88:H94)</f>
+        <v>3155289.5402832869</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="97" spans="1:8" ht="16.5" thickBot="1">
+      <c r="A97" s="201" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="202"/>
+      <c r="C97" s="202"/>
+      <c r="D97" s="202"/>
+      <c r="E97" s="202"/>
+      <c r="F97" s="202"/>
+      <c r="G97" s="202"/>
+      <c r="H97" s="203"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75">
+      <c r="A98" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B92" s="147"/>
-      <c r="C92" s="147"/>
-      <c r="D92" s="147"/>
-      <c r="E92" s="147"/>
-      <c r="F92" s="147"/>
-      <c r="G92" s="147"/>
-      <c r="H92" s="148">
-        <v>517126.1110116429</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="82" t="s">
-        <v>141</v>
-      </c>
-      <c r="B93" s="83"/>
-      <c r="C93" s="83"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="83"/>
-      <c r="F93" s="83"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="149">
-        <f>Planilla!G32</f>
-        <v>2164118.5034630927</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" hidden="1">
-      <c r="A94" s="79"/>
-      <c r="B94" s="80"/>
-      <c r="C94" s="80"/>
-      <c r="D94" s="80"/>
-      <c r="E94" s="80"/>
-      <c r="F94" s="80"/>
-      <c r="G94" s="80"/>
-      <c r="H94" s="69"/>
-    </row>
-    <row r="95" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A95" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" s="80"/>
-      <c r="C95" s="80"/>
-      <c r="D95" s="80"/>
-      <c r="E95" s="80"/>
-      <c r="F95" s="80"/>
-      <c r="G95" s="80"/>
-      <c r="H95" s="69">
-        <f>-(H85)</f>
-        <v>-2346651.56</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" hidden="1">
-      <c r="A96" s="79"/>
-      <c r="B96" s="80"/>
-      <c r="C96" s="80"/>
-      <c r="D96" s="80"/>
-      <c r="E96" s="80"/>
-      <c r="F96" s="80"/>
-      <c r="G96" s="80"/>
-      <c r="H96" s="126"/>
-    </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="B97" s="80"/>
-      <c r="C97" s="80"/>
-      <c r="D97" s="80"/>
-      <c r="E97" s="80"/>
-      <c r="F97" s="80"/>
-      <c r="G97" s="80"/>
-      <c r="H97" s="69">
-        <f>-H70</f>
-        <v>-100000</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="B98" s="80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C98" s="80"/>
-      <c r="D98" s="80"/>
-      <c r="E98" s="80"/>
-      <c r="F98" s="80"/>
-      <c r="G98" s="80"/>
-      <c r="H98" s="126">
-        <v>115393.04</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="B99" s="80"/>
-      <c r="C99" s="80"/>
-      <c r="D99" s="80"/>
-      <c r="E99" s="80"/>
-      <c r="F99" s="80"/>
-      <c r="G99" s="80"/>
-      <c r="H99" s="126">
-        <f>60243/2</f>
-        <v>30121.5</v>
-      </c>
-      <c r="I99" s="150"/>
-    </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B100" s="84"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="18">
-      <c r="A101" s="22" t="s">
+      <c r="B98" s="88"/>
+      <c r="C98" s="88"/>
+      <c r="D98" s="88"/>
+      <c r="E98" s="88"/>
+      <c r="F98" s="88"/>
+      <c r="G98" s="88"/>
+      <c r="H98" s="89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" s="92"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="129"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="61"/>
+      <c r="B100" s="98"/>
+      <c r="C100" s="61"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="61"/>
+      <c r="H100" s="21"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="61"/>
+      <c r="B101" s="61"/>
+      <c r="C101" s="61"/>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61"/>
+      <c r="F101" s="61"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="21"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B101" s="23"/>
-      <c r="C101" s="23"/>
-      <c r="D101" s="23"/>
-      <c r="E101" s="23"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="23"/>
-      <c r="H101" s="85">
-        <f>SUM(H92:H100)</f>
-        <v>380107.59447473561</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1"/>
-    <row r="103" spans="1:9" ht="16.2" thickBot="1">
-      <c r="A103" s="196" t="s">
-        <v>105</v>
-      </c>
-      <c r="B103" s="197"/>
-      <c r="C103" s="197"/>
-      <c r="D103" s="197"/>
-      <c r="E103" s="197"/>
-      <c r="F103" s="197"/>
-      <c r="G103" s="197"/>
-      <c r="H103" s="198"/>
-    </row>
-    <row r="104" spans="1:9" ht="15.6">
-      <c r="A104" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" s="88"/>
-      <c r="C104" s="88"/>
-      <c r="D104" s="88"/>
-      <c r="E104" s="88"/>
-      <c r="F104" s="88"/>
-      <c r="G104" s="88"/>
-      <c r="H104" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="B105" s="92"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="61"/>
-      <c r="E105" s="61"/>
-      <c r="F105" s="61"/>
-      <c r="G105" s="61"/>
-      <c r="H105" s="130"/>
-    </row>
-    <row r="106" spans="1:9">
-      <c r="A106" s="61"/>
-      <c r="B106" s="98"/>
-      <c r="C106" s="61"/>
-      <c r="D106" s="61"/>
-      <c r="E106" s="61"/>
-      <c r="F106" s="61"/>
-      <c r="G106" s="61"/>
-      <c r="H106" s="21"/>
-    </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="61"/>
-      <c r="B107" s="61"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="61"/>
-      <c r="E107" s="61"/>
-      <c r="F107" s="61"/>
-      <c r="G107" s="61"/>
-      <c r="H107" s="21"/>
-    </row>
-    <row r="108" spans="1:9">
-      <c r="A108" s="86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B108" s="86"/>
-      <c r="C108" s="86"/>
-      <c r="D108" s="86"/>
-      <c r="E108" s="86"/>
-      <c r="F108" s="86"/>
-      <c r="G108" s="86"/>
-      <c r="H108" s="87">
-        <f>SUM(H104:H107)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" hidden="1">
-      <c r="A111" s="195"/>
-      <c r="B111" s="195"/>
-      <c r="C111" s="195"/>
-      <c r="D111" s="195"/>
-      <c r="E111" s="195"/>
-      <c r="F111" s="195"/>
-      <c r="G111" s="195"/>
-      <c r="H111" s="195"/>
-    </row>
-    <row r="112" spans="1:9" hidden="1">
-      <c r="A112" s="195"/>
-      <c r="B112" s="195"/>
-      <c r="C112" s="195"/>
-      <c r="D112" s="195"/>
-      <c r="E112" s="195"/>
-      <c r="F112" s="195"/>
-      <c r="G112" s="195"/>
-      <c r="H112" s="195"/>
-    </row>
-    <row r="113" spans="1:8" hidden="1">
-      <c r="A113" s="195"/>
-      <c r="B113" s="195"/>
-      <c r="C113" s="195"/>
-      <c r="D113" s="195"/>
-      <c r="E113" s="195"/>
-      <c r="F113" s="195"/>
-      <c r="G113" s="195"/>
-      <c r="H113" s="195"/>
-    </row>
-    <row r="114" spans="1:8" hidden="1">
-      <c r="A114" s="195"/>
-      <c r="B114" s="195"/>
-      <c r="C114" s="195"/>
-      <c r="D114" s="195"/>
-      <c r="E114" s="195"/>
-      <c r="F114" s="195"/>
-      <c r="G114" s="195"/>
-      <c r="H114" s="195"/>
+      <c r="B102" s="86"/>
+      <c r="C102" s="86"/>
+      <c r="D102" s="86"/>
+      <c r="E102" s="86"/>
+      <c r="F102" s="86"/>
+      <c r="G102" s="86"/>
+      <c r="H102" s="87">
+        <f>SUM(H98:H101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1">
+      <c r="A105" s="186"/>
+      <c r="B105" s="186"/>
+      <c r="C105" s="186"/>
+      <c r="D105" s="186"/>
+      <c r="E105" s="186"/>
+      <c r="F105" s="186"/>
+      <c r="G105" s="186"/>
+      <c r="H105" s="186"/>
+    </row>
+    <row r="106" spans="1:8" hidden="1">
+      <c r="A106" s="186"/>
+      <c r="B106" s="186"/>
+      <c r="C106" s="186"/>
+      <c r="D106" s="186"/>
+      <c r="E106" s="186"/>
+      <c r="F106" s="186"/>
+      <c r="G106" s="186"/>
+      <c r="H106" s="186"/>
+    </row>
+    <row r="107" spans="1:8" hidden="1">
+      <c r="A107" s="186"/>
+      <c r="B107" s="186"/>
+      <c r="C107" s="186"/>
+      <c r="D107" s="186"/>
+      <c r="E107" s="186"/>
+      <c r="F107" s="186"/>
+      <c r="G107" s="186"/>
+      <c r="H107" s="186"/>
+    </row>
+    <row r="108" spans="1:8" hidden="1">
+      <c r="A108" s="186"/>
+      <c r="B108" s="186"/>
+      <c r="C108" s="186"/>
+      <c r="D108" s="186"/>
+      <c r="E108" s="186"/>
+      <c r="F108" s="186"/>
+      <c r="G108" s="186"/>
+      <c r="H108" s="186"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A105:H108"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A69:H70"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A77:G77"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A83:G83"/>
-    <mergeCell ref="A85:G85"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A71:H72"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="A111:H114"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A80:G80"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
